--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487199_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487199_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5634</v>
+        <v>6.3833</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9479</v>
+        <v>6.7679</v>
       </c>
       <c r="F2" t="n">
         <v>-0.3845</v>
@@ -610,10 +610,10 @@
         <v>2.7021</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.2117</v>
+        <v>-1.3917</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.4277</v>
+        <v>-0.6077</v>
       </c>
       <c r="U2" t="n">
         <v>-0.784</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.477</v>
+        <v>3.597</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7716</v>
+        <v>1.7309</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7054</v>
+        <v>1.8661</v>
       </c>
       <c r="G3" t="n">
         <v>4.1744</v>
@@ -688,13 +688,13 @@
         <v>2.1231</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8289</v>
+        <v>-0.7089</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0912</v>
+        <v>-0.1318</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7377</v>
+        <v>-0.5770999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>-1.0266</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6476</v>
+        <v>3.3486</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4741</v>
+        <v>0.9341</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1735</v>
+        <v>2.4144</v>
       </c>
       <c r="G4" t="n">
         <v>3.2502</v>
@@ -766,13 +766,13 @@
         <v>1.9301</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.5024</v>
+        <v>-0.8015</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8183</v>
+        <v>-0.3582</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6841</v>
+        <v>-0.4432</v>
       </c>
       <c r="V4" t="n">
         <v>0.8999</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9827</v>
+        <v>2.1691</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8179</v>
+        <v>1.9775</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1649</v>
+        <v>0.1916</v>
       </c>
       <c r="G5" t="n">
         <v>-0.3773</v>
@@ -844,13 +844,13 @@
         <v>2.3161</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8137</v>
+        <v>-0.6273</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2102</v>
+        <v>-0.0505</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6035</v>
+        <v>-0.5767</v>
       </c>
       <c r="V5" t="n">
         <v>0.8576</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.078</v>
+        <v>0.383</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0826</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0046</v>
+        <v>-0.299</v>
       </c>
       <c r="G6" t="n">
         <v>-0.8969</v>
@@ -922,13 +922,13 @@
         <v>0.579</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7396</v>
+        <v>0.0446</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3847</v>
+        <v>-0.0159</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3549</v>
+        <v>0.0605</v>
       </c>
       <c r="V6" t="n">
         <v>0.6562</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.072</v>
+        <v>-1.1116</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0735</v>
+        <v>0.8732</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.1455</v>
+        <v>-1.9849</v>
       </c>
       <c r="G7" t="n">
         <v>0.3084</v>
@@ -1000,13 +1000,13 @@
         <v>1.3511</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4733</v>
+        <v>-0.5129</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0278</v>
+        <v>-0.1725</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.501</v>
+        <v>-0.3404</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3281</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.9377</v>
+        <v>-3.5048</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7967</v>
+        <v>-1.4976</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.1411</v>
+        <v>-2.0072</v>
       </c>
       <c r="G8" t="n">
         <v>-2.9067</v>
@@ -1078,13 +1078,13 @@
         <v>0.386</v>
       </c>
       <c r="S8" t="n">
-        <v>0.548</v>
+        <v>-0.0192</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7998</v>
+        <v>0.0988</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2518</v>
+        <v>-0.118</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.7348</v>
+        <v>-4.1281</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.0336</v>
+        <v>-2.6142</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.7012</v>
+        <v>-1.5139</v>
       </c>
       <c r="G9" t="n">
         <v>-3.2113</v>
@@ -1156,13 +1156,13 @@
         <v>1.3511</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.9096</v>
+        <v>-1.3028</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8923</v>
+        <v>-0.4729</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.0173</v>
+        <v>-0.8299</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.4538</v>
+        <v>-6.1285</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.1552</v>
+        <v>-5.5355</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2985</v>
+        <v>-0.593</v>
       </c>
       <c r="G10" t="n">
         <v>-1.2301</v>
@@ -1234,13 +1234,13 @@
         <v>2.5091</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6796</v>
+        <v>-1.3544</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.3682</v>
+        <v>-0.7485000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3114</v>
+        <v>-0.6058</v>
       </c>
       <c r="V10" t="n">
         <v>-1.228</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.7134</v>
+        <v>-7.576</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.4106</v>
+        <v>-4.952</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.3028</v>
+        <v>-2.624</v>
       </c>
       <c r="G11" t="n">
         <v>-3.2671</v>
@@ -1312,13 +1312,13 @@
         <v>1.158</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4838</v>
+        <v>-0.3787</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3834</v>
+        <v>-0.158</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1004</v>
+        <v>-0.2208</v>
       </c>
       <c r="V11" t="n">
         <v>-1.228</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.162999999999999</v>
+        <v>-6.568</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2285</v>
+        <v>-1.6337</v>
       </c>
       <c r="F12" t="n">
         <v>-4.9344</v>
@@ -1390,13 +1390,13 @@
         <v>16.4057</v>
       </c>
       <c r="S12" t="n">
-        <v>-7.6478</v>
+        <v>-7.0528</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.2122</v>
+        <v>-2.6172</v>
       </c>
       <c r="U12" t="n">
-        <v>-4.435500000000001</v>
+        <v>-4.4354</v>
       </c>
       <c r="V12" t="n">
         <v>-2.011</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.1464</v>
+        <v>2.8589</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.107</v>
+        <v>-0.2071</v>
       </c>
       <c r="F13" t="n">
-        <v>3.2534</v>
+        <v>3.066</v>
       </c>
       <c r="G13" t="n">
         <v>1.9979</v>
@@ -1468,13 +1468,13 @@
         <v>2.1231</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7079</v>
+        <v>0.4204</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0462</v>
+        <v>-0.1464</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7542</v>
+        <v>0.5668</v>
       </c>
       <c r="V13" t="n">
         <v>0.2476</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>U. PEREZ SANZ</t>
+          <t>E. HUIZI ZUBELDIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.0751</v>
+        <v>2.6772</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5493</v>
+        <v>2.5588</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5256999999999999</v>
+        <v>0.1184</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5342</v>
+        <v>1.6186</v>
       </c>
       <c r="H14" t="n">
-        <v>1.7801</v>
+        <v>1.0909</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.2459</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>2.2153</v>
+        <v>4.1201</v>
       </c>
       <c r="K14" t="n">
-        <v>2.3545</v>
+        <v>1.5317</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.1392</v>
+        <v>2.5883</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.6811</v>
+        <v>-2.5015</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5743</v>
+        <v>-0.4408</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.1067</v>
+        <v>-2.0607</v>
       </c>
       <c r="P14" t="n">
-        <v>0.965</v>
+        <v>0.579</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R14" t="n">
-        <v>1.9301</v>
+        <v>2.5091</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6987</v>
+        <v>0.8461</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0132</v>
+        <v>0.3689</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6854</v>
+        <v>0.4772</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.1228</v>
+        <v>-0.3664</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.4087</v>
+        <v>-0.3664</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. HUIZI ZUBELDIA</t>
+          <t>A. GORDILLO BELTRAN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.929</v>
+        <v>2.4664</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1583</v>
+        <v>2.2403</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2293</v>
+        <v>0.226</v>
       </c>
       <c r="G15" t="n">
-        <v>1.6186</v>
+        <v>-1.1761</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0909</v>
+        <v>-0.0073</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5276999999999999</v>
+        <v>-1.1689</v>
       </c>
       <c r="J15" t="n">
-        <v>4.1201</v>
+        <v>1.1254</v>
       </c>
       <c r="K15" t="n">
-        <v>1.5317</v>
+        <v>0.507</v>
       </c>
       <c r="L15" t="n">
-        <v>2.5883</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.5015</v>
+        <v>-2.3015</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4408</v>
+        <v>-0.5143</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.0607</v>
+        <v>-1.7872</v>
       </c>
       <c r="P15" t="n">
-        <v>0.579</v>
+        <v>1.9301</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.5091</v>
+        <v>1.9301</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0978</v>
+        <v>0.1563</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0317</v>
+        <v>-0.113</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1295</v>
+        <v>0.2693</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.3664</v>
+        <v>1.5561</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.3664</v>
+        <v>0.3281</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. GORDILLO BELTRAN</t>
+          <t>U. PEREZ SANZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8387</v>
+        <v>2.3418</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6395</v>
+        <v>1.9499</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1992</v>
+        <v>0.3919</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.1761</v>
+        <v>0.5342</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0073</v>
+        <v>1.7801</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.1689</v>
+        <v>-1.2459</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1254</v>
+        <v>2.2153</v>
       </c>
       <c r="K16" t="n">
-        <v>0.507</v>
+        <v>2.3545</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6183999999999999</v>
+        <v>-0.1392</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.3015</v>
+        <v>-1.6811</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5143</v>
+        <v>-0.5743</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.7872</v>
+        <v>-1.1067</v>
       </c>
       <c r="P16" t="n">
-        <v>1.9301</v>
+        <v>0.965</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R16" t="n">
         <v>1.9301</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4713</v>
+        <v>0.9654</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7139</v>
+        <v>0.4138</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2426</v>
+        <v>0.5516</v>
       </c>
       <c r="V16" t="n">
-        <v>1.5561</v>
+        <v>-0.1228</v>
       </c>
       <c r="W16" t="n">
-        <v>1.228</v>
+        <v>0.2859</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3281</v>
+        <v>-0.4087</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B. ETXEBERRIA AGUIRREZABALA</t>
+          <t>E. ERRASTI URANGA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.7881</v>
+        <v>1.8282</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7383</v>
+        <v>0.635</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0498</v>
+        <v>1.1932</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.491</v>
+        <v>-2.4242</v>
       </c>
       <c r="H17" t="n">
-        <v>2.5615</v>
+        <v>-1.5938</v>
       </c>
       <c r="I17" t="n">
-        <v>-3.0524</v>
+        <v>-0.8304</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5435</v>
+        <v>-1.0504</v>
       </c>
       <c r="K17" t="n">
-        <v>3.3428</v>
+        <v>-1.0661</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.7993</v>
+        <v>0.0157</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.0345</v>
+        <v>-1.3739</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7813</v>
+        <v>-0.5276999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.2531</v>
+        <v>-0.8461</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.3511</v>
+        <v>2.1231</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.8602</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.5091</v>
+        <v>2.1231</v>
       </c>
       <c r="S17" t="n">
-        <v>4.1233</v>
+        <v>1.0242</v>
       </c>
       <c r="T17" t="n">
-        <v>3.4253</v>
+        <v>0.4574</v>
       </c>
       <c r="U17" t="n">
-        <v>0.698</v>
+        <v>0.5668</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.4932</v>
+        <v>1.1052</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3704</v>
+        <v>1.228</v>
       </c>
       <c r="X17" t="n">
         <v>-0.1228</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. ERRASTI URANGA</t>
+          <t>U. CONDE LAKUNTZA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8933</v>
+        <v>1.543</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1661</v>
+        <v>0.784</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0594</v>
+        <v>0.759</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.4242</v>
+        <v>0.1872</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.5938</v>
+        <v>1.8609</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8304</v>
+        <v>-1.6737</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.0504</v>
+        <v>1.6747</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.0661</v>
+        <v>2.3752</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0157</v>
+        <v>-0.7004</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3739</v>
+        <v>-1.4875</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5276999999999999</v>
+        <v>-0.5143</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8461</v>
+        <v>-0.9732</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1231</v>
+        <v>-0.579</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1231</v>
+        <v>1.3511</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0892</v>
+        <v>0.3787</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3437</v>
+        <v>0.1395</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4329</v>
+        <v>0.2393</v>
       </c>
       <c r="V18" t="n">
-        <v>1.1052</v>
+        <v>1.5561</v>
       </c>
       <c r="W18" t="n">
-        <v>1.228</v>
+        <v>0.8999</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1228</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>U. CONDE LAKUNTZA</t>
+          <t>B. ETXEBERRIA AGUIRREZABALA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7016</v>
+        <v>-0.1417</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1832</v>
+        <v>-1.1644</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5184</v>
+        <v>1.0227</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1872</v>
+        <v>-0.491</v>
       </c>
       <c r="H19" t="n">
-        <v>1.8609</v>
+        <v>2.5615</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.6737</v>
+        <v>-3.0524</v>
       </c>
       <c r="J19" t="n">
-        <v>1.6747</v>
+        <v>1.5435</v>
       </c>
       <c r="K19" t="n">
-        <v>2.3752</v>
+        <v>3.3428</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7004</v>
+        <v>-1.7993</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4875</v>
+        <v>-2.0345</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5143</v>
+        <v>-0.7813</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9732</v>
+        <v>-1.2531</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.579</v>
+        <v>-1.3511</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9301</v>
+        <v>-3.8602</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3511</v>
+        <v>2.5091</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4627</v>
+        <v>2.1935</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4614</v>
+        <v>1.5226</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0013</v>
+        <v>0.6709000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>1.5561</v>
+        <v>-0.4932</v>
       </c>
       <c r="W19" t="n">
-        <v>0.8999</v>
+        <v>-0.3704</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6562</v>
+        <v>-0.1228</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9081</v>
+        <v>-1.1484</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0084</v>
+        <v>0.6079</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9166</v>
+        <v>-1.7563</v>
       </c>
       <c r="G20" t="n">
         <v>-1.2805</v>
@@ -2014,13 +2014,13 @@
         <v>1.158</v>
       </c>
       <c r="S20" t="n">
-        <v>1.7391</v>
+        <v>1.4988</v>
       </c>
       <c r="T20" t="n">
-        <v>1.6009</v>
+        <v>1.2004</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1381</v>
+        <v>0.2984</v>
       </c>
       <c r="V20" t="n">
         <v>0.3704</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7741</v>
+        <v>-2.1013</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0969</v>
+        <v>-2.3973</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3228</v>
+        <v>0.296</v>
       </c>
       <c r="G21" t="n">
         <v>0.9953</v>
@@ -2092,13 +2092,13 @@
         <v>0.193</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5466</v>
+        <v>0.2194</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3702</v>
+        <v>0.0697</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1765</v>
+        <v>0.1497</v>
       </c>
       <c r="V21" t="n">
         <v>-0.614</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.527</v>
+        <v>-2.4936</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0274</v>
+        <v>-0.0727</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.5544</v>
+        <v>-2.4209</v>
       </c>
       <c r="G22" t="n">
         <v>-2.4571</v>
@@ -2170,13 +2170,13 @@
         <v>0.579</v>
       </c>
       <c r="S22" t="n">
-        <v>0.579</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6227</v>
+        <v>0.5225</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0436</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="V22" t="n">
         <v>-1.228</v>
@@ -2203,16 +2203,16 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>7.162999999999999</v>
+        <v>7.8305</v>
       </c>
       <c r="E23" t="n">
-        <v>4.9344</v>
+        <v>4.934399999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>2.2284</v>
+        <v>2.895999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.4957</v>
+        <v>-2.495699999999999</v>
       </c>
       <c r="H23" t="n">
         <v>10.3496</v>
@@ -2239,7 +2239,7 @@
         <v>-10.3997</v>
       </c>
       <c r="P23" t="n">
-        <v>-9.999999999998899e-05</v>
+        <v>-0.0001000000000008772</v>
       </c>
       <c r="Q23" t="n">
         <v>-16.4057</v>
@@ -2248,13 +2248,13 @@
         <v>16.4057</v>
       </c>
       <c r="S23" t="n">
-        <v>7.647600000000001</v>
+        <v>8.315200000000001</v>
       </c>
       <c r="T23" t="n">
         <v>4.4354</v>
       </c>
       <c r="U23" t="n">
-        <v>3.2123</v>
+        <v>3.8799</v>
       </c>
       <c r="V23" t="n">
         <v>2.011</v>
